--- a/histograms/histogram_Power__W.xlsx
+++ b/histograms/histogram_Power__W.xlsx
@@ -442,87 +442,87 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134.75</v>
+        <v>122.5</v>
       </c>
       <c r="B2" t="n">
-        <v>16090</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>384.25</v>
+        <v>167.5</v>
       </c>
       <c r="B3" t="n">
-        <v>5366</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>633.75</v>
+        <v>212.5</v>
       </c>
       <c r="B4" t="n">
-        <v>1800</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>883.25</v>
+        <v>257.5</v>
       </c>
       <c r="B5" t="n">
-        <v>1411</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1132.75</v>
+        <v>302.5</v>
       </c>
       <c r="B6" t="n">
-        <v>175</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1382.25</v>
+        <v>347.5</v>
       </c>
       <c r="B7" t="n">
-        <v>639</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1631.75</v>
+        <v>392.5</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1881.25</v>
+        <v>437.5</v>
       </c>
       <c r="B9" t="n">
-        <v>233</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2130.75</v>
+        <v>482.5</v>
       </c>
       <c r="B10" t="n">
-        <v>309</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2380.25</v>
+        <v>527.5</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2629.75</v>
+        <v>572.5</v>
       </c>
       <c r="B12" t="n">
         <v>0</v>
@@ -530,15 +530,15 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2879.25</v>
+        <v>617.5</v>
       </c>
       <c r="B13" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3128.75</v>
+        <v>662.5</v>
       </c>
       <c r="B14" t="n">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3378.25</v>
+        <v>707.5</v>
       </c>
       <c r="B15" t="n">
         <v>0</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3627.75</v>
+        <v>752.5</v>
       </c>
       <c r="B16" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3877.25</v>
+        <v>797.5</v>
       </c>
       <c r="B17" t="n">
         <v>0</v>
@@ -570,7 +570,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>4126.75</v>
+        <v>842.5</v>
       </c>
       <c r="B18" t="n">
         <v>0</v>
@@ -578,7 +578,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>4376.25</v>
+        <v>887.5</v>
       </c>
       <c r="B19" t="n">
         <v>0</v>
@@ -586,7 +586,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>4625.75</v>
+        <v>932.5</v>
       </c>
       <c r="B20" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>4875.25</v>
+        <v>977.5</v>
       </c>
       <c r="B21" t="n">
-        <v>132</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
